--- a/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
@@ -662,19 +662,19 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>78.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>21.1</v>
+        <v>18.4</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -834,19 +834,19 @@
         <v>254</v>
       </c>
       <c r="E11">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F11">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" s="1">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="H11" s="1">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="I11" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -997,16 +997,16 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F16">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G16" s="1">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
       <c r="H16" s="1">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="I16" s="2">
         <v>5.6</v>
@@ -1083,25 +1083,25 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1118,25 +1118,25 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>25.6</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>35.5</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1223,25 +1223,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1258,25 +1258,25 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>44.8</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>55.2</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1293,25 +1293,25 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>60.9</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>39.1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1328,25 +1328,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1363,25 +1363,25 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1395,25 +1395,25 @@
         <v>254</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="F11">
-        <v>254</v>
+        <v>88</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>34.6</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>43.3</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>56.7</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>43.3</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>56.7</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="F16">
-        <v>319</v>
+        <v>140</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>56.1</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>43.9</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J16">
-        <v>319</v>
+        <v>35</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1656,7 +1656,7 @@
         <v>60</v>
       </c>
       <c r="I2" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1679,19 +1679,19 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>76.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>23.1</v>
+        <v>25.6</v>
       </c>
       <c r="I3" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>35.5</v>
       </c>
       <c r="I4" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>78.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>21.1</v>
+        <v>7.9</v>
       </c>
       <c r="I6" s="2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" s="1">
-        <v>37.9</v>
+        <v>44.8</v>
       </c>
       <c r="H7" s="1">
-        <v>62.1</v>
+        <v>55.2</v>
       </c>
       <c r="I7" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>65.2</v>
+        <v>60.9</v>
       </c>
       <c r="H8" s="1">
-        <v>34.8</v>
+        <v>39.1</v>
       </c>
       <c r="I8" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>33.3</v>
       </c>
       <c r="I9" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="H10" s="1">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="I10" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>254</v>
       </c>
       <c r="E11">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F11">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G11" s="1">
-        <v>63</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>37</v>
+        <v>34.6</v>
       </c>
       <c r="I11" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2058,16 +2058,16 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="H14" s="1">
-        <v>50</v>
+        <v>56.7</v>
       </c>
       <c r="I14" s="2">
         <v>5.5</v>
@@ -2090,16 +2090,16 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="H15" s="1">
-        <v>50</v>
+        <v>56.7</v>
       </c>
       <c r="I15" s="2">
         <v>5.5</v>
@@ -2119,19 +2119,19 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F16">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G16" s="1">
-        <v>54.9</v>
+        <v>56.1</v>
       </c>
       <c r="H16" s="1">
-        <v>45.1</v>
+        <v>43.9</v>
       </c>
       <c r="I16" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>35</v>

--- a/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
@@ -869,25 +869,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -901,25 +901,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -997,25 +997,25 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="F16">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G16" s="1">
-        <v>55.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>44.8</v>
+        <v>35.4</v>
       </c>
       <c r="I16" s="2">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1430,25 +1430,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F16">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G16" s="1">
-        <v>56.1</v>
+        <v>66.5</v>
       </c>
       <c r="H16" s="1">
-        <v>43.9</v>
+        <v>33.5</v>
       </c>
       <c r="I16" s="2">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1991,25 +1991,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2023,25 +2023,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2119,25 +2119,25 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F16">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G16" s="1">
-        <v>56.1</v>
+        <v>66.5</v>
       </c>
       <c r="H16" s="1">
-        <v>43.9</v>
+        <v>33.5</v>
       </c>
       <c r="I16" s="2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
@@ -1644,16 +1644,16 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H2" s="1">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="I2" s="2">
         <v>6.1</v>
@@ -1679,16 +1679,16 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>74.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>25.6</v>
+        <v>15.4</v>
       </c>
       <c r="I3" s="2">
         <v>7.3</v>
@@ -1714,19 +1714,19 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>64.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>35.5</v>
+        <v>22.6</v>
       </c>
       <c r="I4" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>92.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H6" s="1">
-        <v>7.9</v>
+        <v>13.2</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>44.8</v>
+        <v>65.5</v>
       </c>
       <c r="H7" s="1">
-        <v>55.2</v>
+        <v>34.5</v>
       </c>
       <c r="I7" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>60.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>39.1</v>
+        <v>30.4</v>
       </c>
       <c r="I8" s="2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>12</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="H10" s="1">
-        <v>58.3</v>
+        <v>33.3</v>
       </c>
       <c r="I10" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1956,16 +1956,16 @@
         <v>254</v>
       </c>
       <c r="E11">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="F11">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G11" s="1">
-        <v>65.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>34.6</v>
+        <v>26.4</v>
       </c>
       <c r="I11" s="2">
         <v>6.7</v>
@@ -2058,19 +2058,19 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>43.3</v>
+        <v>46.7</v>
       </c>
       <c r="H14" s="1">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="I14" s="2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1">
-        <v>43.3</v>
+        <v>46.7</v>
       </c>
       <c r="H15" s="1">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="I15" s="2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="F16">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="G16" s="1">
-        <v>66.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>33.5</v>
+        <v>26.6</v>
       </c>
       <c r="I16" s="2">
         <v>6.7</v>

--- a/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20232.xlsx
@@ -2003,7 +2003,7 @@
         <v>5.7</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>5.7</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J13">
         <v>0</v>
